--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4114" uniqueCount="568">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1556,10 +1556,7 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-observation-periode-scolaire|2.2.0-ballot</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -8736,13 +8733,11 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y55" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y55" s="2"/>
+      <c r="Z55" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8778,7 +8773,7 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>274</v>
@@ -8795,10 +8790,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8824,13 +8819,13 @@
         <v>334</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>338</v>
@@ -8882,7 +8877,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8900,7 +8895,7 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>341</v>
@@ -8917,10 +8912,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8946,13 +8941,13 @@
         <v>182</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>348</v>
@@ -9004,7 +8999,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9039,10 +9034,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9126,7 +9121,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9161,10 +9156,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9190,10 +9185,10 @@
         <v>83</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>415</v>
@@ -9248,7 +9243,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9283,13 +9278,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>477</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>82</v>
@@ -9407,7 +9402,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>485</v>
@@ -9525,7 +9520,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>486</v>
@@ -9645,7 +9640,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>487</v>
@@ -9767,7 +9762,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>488</v>
@@ -9815,7 +9810,7 @@
         <v>82</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>82</v>
@@ -9830,13 +9825,11 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y64" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y64" s="2"/>
+      <c r="Z64" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9872,7 +9865,7 @@
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>274</v>
@@ -9889,10 +9882,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9918,13 +9911,13 @@
         <v>334</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>338</v>
@@ -9976,7 +9969,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9994,7 +9987,7 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>341</v>
@@ -10011,10 +10004,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10040,13 +10033,13 @@
         <v>182</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>348</v>
@@ -10098,7 +10091,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10133,10 +10126,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10220,7 +10213,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10255,10 +10248,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10284,10 +10277,10 @@
         <v>83</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>415</v>
@@ -10342,7 +10335,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10377,13 +10370,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>477</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>82</v>
@@ -10501,7 +10494,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>485</v>
@@ -10619,7 +10612,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>486</v>
@@ -10739,7 +10732,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>487</v>
@@ -10861,7 +10854,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>488</v>
@@ -10909,7 +10902,7 @@
         <v>82</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>82</v>
@@ -10924,13 +10917,11 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y73" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y73" s="2"/>
+      <c r="Z73" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -10966,7 +10957,7 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>274</v>
@@ -10983,10 +10974,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11012,13 +11003,13 @@
         <v>334</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>338</v>
@@ -11070,7 +11061,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11088,7 +11079,7 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>341</v>
@@ -11105,10 +11096,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11134,13 +11125,13 @@
         <v>182</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>348</v>
@@ -11192,7 +11183,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11227,10 +11218,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11314,7 +11305,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11349,10 +11340,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11378,10 +11369,10 @@
         <v>83</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>415</v>
@@ -11436,7 +11427,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11471,13 +11462,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>477</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11595,7 +11586,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>485</v>
@@ -11713,7 +11704,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>486</v>
@@ -11833,7 +11824,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>487</v>
@@ -11955,7 +11946,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>488</v>
@@ -12003,7 +11994,7 @@
         <v>82</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>82</v>
@@ -12018,13 +12009,11 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y82" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y82" s="2"/>
+      <c r="Z82" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12060,7 +12049,7 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>274</v>
@@ -12077,10 +12066,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12106,13 +12095,13 @@
         <v>334</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M83" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>338</v>
@@ -12152,7 +12141,7 @@
         <v>82</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
@@ -12162,7 +12151,7 @@
         <v>169</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12180,7 +12169,7 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>341</v>
@@ -12197,13 +12186,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
@@ -12228,13 +12217,13 @@
         <v>182</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>338</v>
@@ -12266,7 +12255,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12284,7 +12273,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12302,7 +12291,7 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>341</v>
@@ -12319,10 +12308,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12348,13 +12337,13 @@
         <v>182</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>348</v>
@@ -12406,7 +12395,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12441,10 +12430,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12528,7 +12517,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12563,10 +12552,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12592,10 +12581,10 @@
         <v>83</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>415</v>
@@ -12650,7 +12639,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12685,13 +12674,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>477</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>82</v>
@@ -12809,7 +12798,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>485</v>
@@ -12927,7 +12916,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>486</v>
@@ -13047,7 +13036,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>487</v>
@@ -13169,7 +13158,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>488</v>
@@ -13217,7 +13206,7 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>82</v>
@@ -13232,13 +13221,11 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y92" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y92" s="2"/>
+      <c r="Z92" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13274,7 +13261,7 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>274</v>
@@ -13291,10 +13278,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13320,13 +13307,13 @@
         <v>334</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>338</v>
@@ -13366,7 +13353,7 @@
         <v>82</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
@@ -13376,7 +13363,7 @@
         <v>169</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13394,7 +13381,7 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>341</v>
@@ -13411,13 +13398,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>82</v>
@@ -13442,13 +13429,13 @@
         <v>182</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>338</v>
@@ -13480,7 +13467,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13498,7 +13485,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13516,7 +13503,7 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>341</v>
@@ -13533,10 +13520,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13562,13 +13549,13 @@
         <v>182</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>348</v>
@@ -13620,7 +13607,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13655,10 +13642,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13742,7 +13729,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13777,10 +13764,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13806,10 +13793,10 @@
         <v>83</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>415</v>
@@ -13864,7 +13851,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13899,13 +13886,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>477</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>82</v>
@@ -14023,7 +14010,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>485</v>
@@ -14141,7 +14128,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>486</v>
@@ -14261,7 +14248,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>487</v>
@@ -14383,7 +14370,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>488</v>
@@ -14431,7 +14418,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14446,13 +14433,11 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Y102" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y102" s="2"/>
+      <c r="Z102" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14488,7 +14473,7 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>274</v>
@@ -14505,10 +14490,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14531,16 +14516,16 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>336</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>338</v>
@@ -14592,7 +14577,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14610,7 +14595,7 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>341</v>
@@ -14627,10 +14612,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14656,13 +14641,13 @@
         <v>182</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O104" t="s" s="2">
         <v>348</v>
@@ -14714,7 +14699,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14749,10 +14734,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14836,7 +14821,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14871,10 +14856,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14900,10 +14885,10 @@
         <v>83</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>415</v>
@@ -14958,7 +14943,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -866,7 +866,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-observation-type|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-observation-type</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -890,7 +890,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1562,7 +1562,7 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-observation-periode-scolaire|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-observation-periode-scolaire</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1765,7 +1765,7 @@
     <t>Observation.component:diplome.value[x]:valueCodeableConcept</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS|20230526120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
   </si>
   <si>
     <t>Observation.component:diplome.dataAbsentReason</t>
@@ -2131,7 +2131,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="150.68359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2146,7 +2146,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="88.6171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.08984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="608">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1165,6 +1165,9 @@
 </t>
   </si>
   <si>
+    <t>ReferentScolaire</t>
+  </si>
+  <si>
     <t>Observation.performer:ecole</t>
   </si>
   <si>
@@ -1173,6 +1176,9 @@
   <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
 </t>
+  </si>
+  <si>
+    <t>Ecole</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -6713,7 +6719,7 @@
         <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>83</v>
+        <v>368</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>361</v>
@@ -6736,13 +6742,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>355</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>83</v>
@@ -6764,7 +6770,7 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>357</v>
@@ -6838,7 +6844,7 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>361</v>
@@ -6861,10 +6867,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6887,19 +6893,19 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6948,7 +6954,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6957,7 +6963,7 @@
         <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>107</v>
@@ -6969,27 +6975,27 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7015,16 +7021,16 @@
         <v>185</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7052,10 +7058,10 @@
         <v>190</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -7073,7 +7079,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7082,7 +7088,7 @@
         <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>107</v>
@@ -7100,7 +7106,7 @@
         <v>138</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7111,14 +7117,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7140,16 +7146,16 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7177,10 +7183,10 @@
         <v>190</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7198,7 +7204,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7219,27 +7225,27 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7262,19 +7268,19 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7323,7 +7329,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7338,7 +7344,7 @@
         <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
@@ -7347,10 +7353,10 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7361,10 +7367,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7390,13 +7396,13 @@
         <v>185</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7422,13 +7428,13 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7446,7 +7452,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7467,27 +7473,27 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7513,16 +7519,16 @@
         <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7547,13 +7553,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7571,7 +7577,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7595,10 +7601,10 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7609,10 +7615,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7635,16 +7641,16 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7694,7 +7700,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7715,27 +7721,27 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7758,16 +7764,16 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7817,7 +7823,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7838,27 +7844,27 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7881,19 +7887,19 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7942,7 +7948,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7954,7 +7960,7 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7966,10 +7972,10 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7980,10 +7986,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8101,10 +8107,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8224,14 +8230,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8253,10 +8259,10 @@
         <v>141</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>144</v>
@@ -8311,7 +8317,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8349,10 +8355,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8375,13 +8381,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8432,7 +8438,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8441,7 +8447,7 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
@@ -8456,10 +8462,10 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8470,10 +8476,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8496,13 +8502,13 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8553,7 +8559,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8562,7 +8568,7 @@
         <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>107</v>
@@ -8577,10 +8583,10 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8591,10 +8597,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8620,16 +8626,16 @@
         <v>185</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8657,10 +8663,10 @@
         <v>119</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8678,7 +8684,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8699,13 +8705,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8716,10 +8722,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8745,16 +8751,16 @@
         <v>185</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8779,13 +8785,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8803,7 +8809,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8824,13 +8830,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8841,10 +8847,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8867,17 +8873,17 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8926,7 +8932,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8953,7 +8959,7 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8964,10 +8970,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8993,10 +8999,10 @@
         <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9047,7 +9053,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9071,10 +9077,10 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9085,10 +9091,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9111,16 +9117,16 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9170,7 +9176,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9194,10 +9200,10 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9208,10 +9214,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9234,16 +9240,16 @@
         <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9293,7 +9299,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9317,10 +9323,10 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9331,10 +9337,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9357,19 +9363,19 @@
         <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9406,7 +9412,7 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
@@ -9416,7 +9422,7 @@
         <v>172</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9440,10 +9446,10 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9454,10 +9460,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9575,10 +9581,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9698,14 +9704,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9727,10 +9733,10 @@
         <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>144</v>
@@ -9785,7 +9791,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9823,10 +9829,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9852,13 +9858,13 @@
         <v>185</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>272</v>
@@ -9890,7 +9896,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9908,7 +9914,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>95</v>
@@ -9929,7 +9935,7 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>277</v>
@@ -9946,10 +9952,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9972,19 +9978,19 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10033,7 +10039,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10054,27 +10060,27 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10100,16 +10106,16 @@
         <v>185</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10137,10 +10143,10 @@
         <v>190</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -10158,7 +10164,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10167,7 +10173,7 @@
         <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>107</v>
@@ -10185,7 +10191,7 @@
         <v>138</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10196,14 +10202,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10225,16 +10231,16 @@
         <v>185</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10262,10 +10268,10 @@
         <v>190</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10283,7 +10289,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10304,27 +10310,27 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10350,16 +10356,16 @@
         <v>84</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10408,7 +10414,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10432,10 +10438,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10446,13 +10452,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>83</v>
@@ -10474,19 +10480,19 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10535,7 +10541,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10550,7 +10556,7 @@
         <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -10559,10 +10565,10 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10573,10 +10579,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10694,10 +10700,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10817,14 +10823,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10846,10 +10852,10 @@
         <v>141</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>144</v>
@@ -10904,7 +10910,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10942,10 +10948,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10971,13 +10977,13 @@
         <v>185</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>272</v>
@@ -10990,7 +10996,7 @@
         <v>83</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>83</v>
@@ -11009,7 +11015,7 @@
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -11027,7 +11033,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>95</v>
@@ -11048,7 +11054,7 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>277</v>
@@ -11065,10 +11071,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11091,19 +11097,19 @@
         <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11152,7 +11158,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11173,27 +11179,27 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11219,16 +11225,16 @@
         <v>185</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11256,10 +11262,10 @@
         <v>190</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -11277,7 +11283,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11286,7 +11292,7 @@
         <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>107</v>
@@ -11304,7 +11310,7 @@
         <v>138</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
@@ -11315,14 +11321,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11344,16 +11350,16 @@
         <v>185</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11381,10 +11387,10 @@
         <v>190</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11402,7 +11408,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11423,27 +11429,27 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11469,16 +11475,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11527,7 +11533,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11551,10 +11557,10 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -11565,13 +11571,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>83</v>
@@ -11593,19 +11599,19 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11654,7 +11660,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11669,7 +11675,7 @@
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>83</v>
@@ -11678,10 +11684,10 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -11692,10 +11698,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11813,10 +11819,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11936,14 +11942,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11965,10 +11971,10 @@
         <v>141</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>144</v>
@@ -12023,7 +12029,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12061,10 +12067,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12090,13 +12096,13 @@
         <v>185</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O80" t="s" s="2">
         <v>272</v>
@@ -12109,7 +12115,7 @@
         <v>83</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>83</v>
@@ -12128,7 +12134,7 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12146,7 +12152,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>95</v>
@@ -12167,7 +12173,7 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>277</v>
@@ -12184,10 +12190,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12210,19 +12216,19 @@
         <v>96</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12271,7 +12277,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12292,27 +12298,27 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12338,16 +12344,16 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12375,10 +12381,10 @@
         <v>190</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12396,7 +12402,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12405,7 +12411,7 @@
         <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>107</v>
@@ -12423,7 +12429,7 @@
         <v>138</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12434,14 +12440,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12463,16 +12469,16 @@
         <v>185</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12500,10 +12506,10 @@
         <v>190</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12521,7 +12527,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12542,27 +12548,27 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12588,16 +12594,16 @@
         <v>84</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12646,7 +12652,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12670,10 +12676,10 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12684,13 +12690,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>83</v>
@@ -12712,19 +12718,19 @@
         <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12773,7 +12779,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12788,7 +12794,7 @@
         <v>107</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>83</v>
@@ -12797,10 +12803,10 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -12811,10 +12817,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12932,10 +12938,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13055,14 +13061,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13084,10 +13090,10 @@
         <v>141</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>144</v>
@@ -13142,7 +13148,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13180,10 +13186,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13209,13 +13215,13 @@
         <v>185</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>272</v>
@@ -13228,7 +13234,7 @@
         <v>83</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>83</v>
@@ -13247,7 +13253,7 @@
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13265,7 +13271,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>95</v>
@@ -13286,7 +13292,7 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>277</v>
@@ -13303,10 +13309,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13329,19 +13335,19 @@
         <v>96</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13388,7 +13394,7 @@
         <v>172</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13409,30 +13415,30 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>83</v>
@@ -13457,16 +13463,16 @@
         <v>185</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13495,7 +13501,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13513,7 +13519,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13534,27 +13540,27 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13580,16 +13586,16 @@
         <v>185</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13617,10 +13623,10 @@
         <v>190</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13638,7 +13644,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13647,7 +13653,7 @@
         <v>95</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>107</v>
@@ -13665,7 +13671,7 @@
         <v>138</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -13676,14 +13682,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13705,16 +13711,16 @@
         <v>185</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13742,10 +13748,10 @@
         <v>190</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13763,7 +13769,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13784,27 +13790,27 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13830,16 +13836,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13888,7 +13894,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13912,10 +13918,10 @@
         <v>83</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13926,13 +13932,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>83</v>
@@ -13954,19 +13960,19 @@
         <v>96</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -14015,7 +14021,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14030,7 +14036,7 @@
         <v>107</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>83</v>
@@ -14039,10 +14045,10 @@
         <v>83</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -14053,10 +14059,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14174,10 +14180,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14297,14 +14303,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14326,10 +14332,10 @@
         <v>141</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>144</v>
@@ -14384,7 +14390,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14422,10 +14428,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14451,13 +14457,13 @@
         <v>185</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>272</v>
@@ -14470,7 +14476,7 @@
         <v>83</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>83</v>
@@ -14489,7 +14495,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14507,7 +14513,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>95</v>
@@ -14528,7 +14534,7 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>277</v>
@@ -14545,10 +14551,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14571,19 +14577,19 @@
         <v>96</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
@@ -14630,7 +14636,7 @@
         <v>172</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14651,30 +14657,30 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
@@ -14699,16 +14705,16 @@
         <v>185</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14737,7 +14743,7 @@
       </c>
       <c r="Y101" s="2"/>
       <c r="Z101" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>83</v>
@@ -14755,7 +14761,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14776,27 +14782,27 @@
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14822,16 +14828,16 @@
         <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14859,10 +14865,10 @@
         <v>190</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>83</v>
@@ -14880,7 +14886,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14889,7 +14895,7 @@
         <v>95</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>107</v>
@@ -14907,7 +14913,7 @@
         <v>138</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -14918,14 +14924,14 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14947,16 +14953,16 @@
         <v>185</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14984,10 +14990,10 @@
         <v>190</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -15005,7 +15011,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15026,27 +15032,27 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15072,16 +15078,16 @@
         <v>84</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15130,7 +15136,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15154,10 +15160,10 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>83</v>
@@ -15168,13 +15174,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>83</v>
@@ -15196,19 +15202,19 @@
         <v>96</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15257,7 +15263,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15272,7 +15278,7 @@
         <v>107</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>83</v>
@@ -15281,10 +15287,10 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
@@ -15295,10 +15301,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15416,10 +15422,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15539,14 +15545,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15568,10 +15574,10 @@
         <v>141</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>144</v>
@@ -15626,7 +15632,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15664,10 +15670,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15693,13 +15699,13 @@
         <v>185</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>272</v>
@@ -15712,7 +15718,7 @@
         <v>83</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>83</v>
@@ -15731,7 +15737,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15749,7 +15755,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>95</v>
@@ -15770,7 +15776,7 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>277</v>
@@ -15787,10 +15793,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15813,19 +15819,19 @@
         <v>96</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15874,7 +15880,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15895,27 +15901,27 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15941,16 +15947,16 @@
         <v>185</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15978,10 +15984,10 @@
         <v>190</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15999,7 +16005,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16008,7 +16014,7 @@
         <v>95</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>107</v>
@@ -16026,7 +16032,7 @@
         <v>138</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
@@ -16037,14 +16043,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16066,16 +16072,16 @@
         <v>185</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -16103,10 +16109,10 @@
         <v>190</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16124,7 +16130,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16145,27 +16151,27 @@
         <v>83</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ112" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16191,16 +16197,16 @@
         <v>84</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -16249,7 +16255,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16273,10 +16279,10 @@
         <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="586">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1728,84 +1728,6 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel</t>
-  </si>
-  <si>
-    <t>niveauScolaireReel</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.id</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-observation-periode-scolaire"/&gt;
-    &lt;code value="niveauScolaireReel"/&gt;
-    &lt;display value="Niveau scolaire réel"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireReel.referenceRange</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi</t>
-  </si>
-  <si>
-    <t>niveauScolaireSuivi</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.id</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-observation-periode-scolaire"/&gt;
-    &lt;code value="niveauScolaireSuivi"/&gt;
-    &lt;display value="Niveau scolaire suivi"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:niveauScolaireSuivi.referenceRange</t>
   </si>
   <si>
     <t>Observation.component:typeEnseignementSpecialise</t>
@@ -2243,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ113"/>
+  <dimension ref="A1:AQ95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.7265625" customWidth="true" bestFit="true"/>
@@ -4158,7 +4080,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>95</v>
@@ -4283,7 +4205,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>95</v>
@@ -10468,7 +10390,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>83</v>
@@ -11146,16 +11068,14 @@
         <v>83</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="AC72" s="2"/>
       <c r="AD72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>535</v>
@@ -11199,9 +11119,11 @@
         <v>555</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>83</v>
       </c>
@@ -11219,22 +11141,22 @@
         <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>541</v>
+        <v>376</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11259,13 +11181,11 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>390</v>
+        <v>557</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -11283,7 +11203,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11292,7 +11212,7 @@
         <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>107</v>
@@ -11304,38 +11224,38 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>83</v>
+        <v>538</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>138</v>
+        <v>381</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
@@ -11350,16 +11270,16 @@
         <v>185</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>395</v>
+        <v>540</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>396</v>
+        <v>541</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>397</v>
+        <v>542</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11387,10 +11307,10 @@
         <v>190</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11408,16 +11328,16 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>107</v>
@@ -11429,31 +11349,31 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>402</v>
+        <v>138</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11472,19 +11392,19 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>545</v>
+        <v>395</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>546</v>
+        <v>396</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>456</v>
+        <v>397</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>457</v>
+        <v>398</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11509,13 +11429,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11533,7 +11453,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11554,31 +11474,29 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11587,7 +11505,7 @@
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>83</v>
@@ -11596,22 +11514,22 @@
         <v>83</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>521</v>
+        <v>456</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>522</v>
+        <v>457</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11660,7 +11578,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11675,7 +11593,7 @@
         <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>559</v>
+        <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>83</v>
@@ -11684,10 +11602,10 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>524</v>
+        <v>459</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>525</v>
+        <v>460</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -11698,12 +11616,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
       </c>
@@ -11712,7 +11632,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11721,19 +11641,23 @@
         <v>83</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>163</v>
+        <v>453</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>164</v>
+        <v>519</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
       </c>
@@ -11781,22 +11705,22 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>166</v>
+        <v>518</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>83</v>
+        <v>562</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>83</v>
@@ -11805,10 +11729,10 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>83</v>
+        <v>524</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>167</v>
+        <v>525</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>83</v>
@@ -11819,21 +11743,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
@@ -11845,17 +11769,15 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11904,19 +11826,19 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11942,14 +11864,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>464</v>
+        <v>140</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11962,26 +11884,24 @@
         <v>83</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>465</v>
+        <v>142</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>466</v>
+        <v>169</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="O79" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -12029,7 +11949,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>467</v>
+        <v>173</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12056,7 +11976,7 @@
         <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -12067,45 +11987,45 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>530</v>
+        <v>465</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>531</v>
+        <v>466</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>532</v>
+        <v>144</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>272</v>
+        <v>150</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12115,7 +12035,7 @@
         <v>83</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>564</v>
+        <v>83</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>83</v>
@@ -12130,11 +12050,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>533</v>
+        <v>83</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12152,19 +12074,19 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>529</v>
+        <v>467</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -12173,16 +12095,16 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>83</v>
@@ -12190,10 +12112,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12201,7 +12123,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>95</v>
@@ -12216,19 +12138,19 @@
         <v>96</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>374</v>
+        <v>185</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>376</v>
+        <v>531</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>378</v>
+        <v>272</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12238,7 +12160,7 @@
         <v>83</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>83</v>
+        <v>567</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>83</v>
@@ -12253,13 +12175,11 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>533</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12277,10 +12197,10 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>95</v>
@@ -12298,27 +12218,27 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>381</v>
+        <v>277</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>382</v>
+        <v>278</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12338,22 +12258,22 @@
         <v>83</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>185</v>
+        <v>374</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>541</v>
+        <v>376</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12378,31 +12298,29 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12411,7 +12329,7 @@
         <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>107</v>
@@ -12423,38 +12341,40 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>83</v>
+        <v>538</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>138</v>
+        <v>381</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="D83" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12463,22 +12383,22 @@
         <v>83</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>395</v>
+        <v>536</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>397</v>
+        <v>537</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12503,13 +12423,11 @@
         <v>83</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>400</v>
+        <v>570</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12527,13 +12445,13 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
@@ -12548,27 +12466,27 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>401</v>
+        <v>538</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>404</v>
+        <v>383</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12579,7 +12497,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12591,19 +12509,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>456</v>
+        <v>542</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>457</v>
+        <v>388</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12628,13 +12546,13 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12652,16 +12570,16 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>107</v>
@@ -12676,10 +12594,10 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>459</v>
+        <v>138</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>460</v>
+        <v>392</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12690,16 +12608,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12715,22 +12631,22 @@
         <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>453</v>
+        <v>185</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>519</v>
+        <v>395</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>520</v>
+        <v>396</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>521</v>
+        <v>397</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>522</v>
+        <v>398</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12755,13 +12671,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12779,7 +12695,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12794,33 +12710,33 @@
         <v>107</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>570</v>
+        <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>524</v>
+        <v>402</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>525</v>
+        <v>403</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12831,7 +12747,7 @@
         <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>83</v>
@@ -12843,16 +12759,20 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>164</v>
+        <v>545</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12900,19 +12820,19 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>166</v>
+        <v>544</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12924,10 +12844,10 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>167</v>
+        <v>460</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -12938,21 +12858,23 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="D87" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
@@ -12961,21 +12883,23 @@
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>141</v>
+        <v>453</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>142</v>
+        <v>519</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>169</v>
+        <v>520</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -13023,7 +12947,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>173</v>
+        <v>518</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13035,10 +12959,10 @@
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>83</v>
+        <v>575</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>83</v>
@@ -13047,10 +12971,10 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>83</v>
+        <v>524</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>167</v>
+        <v>525</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -13061,46 +12985,42 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>464</v>
+        <v>83</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>465</v>
+        <v>164</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>83</v>
       </c>
@@ -13148,19 +13068,19 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>467</v>
+        <v>166</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13175,7 +13095,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13186,21 +13106,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -13209,23 +13129,21 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>530</v>
+        <v>142</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>531</v>
+        <v>169</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13234,7 +13152,7 @@
         <v>83</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>575</v>
+        <v>83</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>83</v>
@@ -13249,11 +13167,13 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y89" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z89" t="s" s="2">
-        <v>533</v>
+        <v>83</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13271,19 +13191,19 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>529</v>
+        <v>173</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
@@ -13292,16 +13212,16 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>278</v>
+        <v>167</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13309,45 +13229,45 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>374</v>
+        <v>141</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>536</v>
+        <v>465</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>376</v>
+        <v>466</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>537</v>
+        <v>144</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>378</v>
+        <v>150</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13384,29 +13304,31 @@
         <v>83</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AC90" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>535</v>
+        <v>467</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
@@ -13415,37 +13337,35 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>382</v>
+        <v>138</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>95</v>
@@ -13463,16 +13383,16 @@
         <v>185</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>376</v>
+        <v>531</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>378</v>
+        <v>272</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13482,7 +13402,7 @@
         <v>83</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>83</v>
@@ -13501,7 +13421,7 @@
       </c>
       <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>579</v>
+        <v>533</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13519,10 +13439,10 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>95</v>
@@ -13540,27 +13460,27 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>381</v>
+        <v>277</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>382</v>
+        <v>278</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13580,22 +13500,22 @@
         <v>83</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>185</v>
+        <v>582</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>541</v>
+        <v>376</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13620,13 +13540,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13644,7 +13564,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13653,7 +13573,7 @@
         <v>95</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>107</v>
@@ -13665,38 +13585,38 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>83</v>
+        <v>538</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>138</v>
+        <v>381</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>83</v>
@@ -13711,16 +13631,16 @@
         <v>185</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>395</v>
+        <v>540</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>396</v>
+        <v>541</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>397</v>
+        <v>542</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13748,10 +13668,10 @@
         <v>190</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13769,16 +13689,16 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>107</v>
@@ -13790,31 +13710,31 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>402</v>
+        <v>138</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13833,19 +13753,19 @@
         <v>83</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>545</v>
+        <v>395</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>546</v>
+        <v>396</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>456</v>
+        <v>397</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>457</v>
+        <v>398</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13870,13 +13790,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13894,7 +13814,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13915,31 +13835,29 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13957,22 +13875,22 @@
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>521</v>
+        <v>456</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>522</v>
+        <v>457</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -14021,7 +13939,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14036,7 +13954,7 @@
         <v>107</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>584</v>
+        <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>83</v>
@@ -14045,2249 +13963,15 @@
         <v>83</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>524</v>
+        <v>459</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>525</v>
+        <v>460</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y99" s="2"/>
-      <c r="Z99" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AC100" s="2"/>
-      <c r="AD100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ100" t="s" s="2">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="D101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y101" s="2"/>
-      <c r="Z101" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ104" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="D105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y109" s="2"/>
-      <c r="Z109" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ110" t="s" s="2">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ111" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ112" t="s" s="2">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ113" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="617">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1693,6 +1693,64 @@
 &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1757,6 +1815,18 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Observation.component:typeEnseignementSpecialise.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:typeEnseignementSpecialise.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:typeEnseignementSpecialise.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:typeEnseignementSpecialise.code.text</t>
+  </si>
+  <si>
     <t>Observation.component:typeEnseignementSpecialise.value[x]</t>
   </si>
   <si>
@@ -1805,6 +1875,18 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Observation.component:diplome.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:diplome.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:diplome.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:diplome.code.text</t>
+  </si>
+  <si>
     <t>Observation.component:diplome.value[x]</t>
   </si>
   <si>
@@ -1848,6 +1930,18 @@
     &lt;display value="Volume de scolarisation"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:volumeScolarisation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:volumeScolarisation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:volumeScolarisation.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:volumeScolarisation.code.text</t>
   </si>
   <si>
     <t>Observation.component:volumeScolarisation.value[x]</t>
@@ -2165,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ95"/>
+  <dimension ref="A1:AQ111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.7265625" customWidth="true" bestFit="true"/>
@@ -9897,23 +9991,19 @@
         <v>83</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>374</v>
+        <v>163</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>536</v>
+        <v>164</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -9961,7 +10051,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>535</v>
+        <v>166</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9973,7 +10063,7 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -9982,38 +10072,38 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>382</v>
+        <v>167</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -10025,20 +10115,18 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>540</v>
+        <v>142</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>541</v>
+        <v>169</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -10062,43 +10150,43 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>539</v>
+        <v>173</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>83</v>
@@ -10110,10 +10198,10 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>392</v>
+        <v>167</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10124,21 +10212,21 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>83</v>
@@ -10147,22 +10235,22 @@
         <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>185</v>
+        <v>538</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>395</v>
+        <v>539</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>396</v>
+        <v>540</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>397</v>
+        <v>541</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>398</v>
+        <v>542</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10187,13 +10275,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10232,27 +10320,27 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>402</v>
+        <v>544</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>403</v>
+        <v>545</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10263,7 +10351,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -10272,22 +10360,22 @@
         <v>83</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>456</v>
+        <v>549</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>457</v>
+        <v>550</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10336,13 +10424,13 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
@@ -10360,10 +10448,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>459</v>
+        <v>552</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>460</v>
+        <v>553</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10374,23 +10462,21 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>83</v>
@@ -10402,19 +10488,19 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>453</v>
+        <v>374</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>520</v>
+        <v>376</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>521</v>
+        <v>556</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>522</v>
+        <v>378</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10463,13 +10549,13 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>83</v>
@@ -10478,33 +10564,33 @@
         <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>548</v>
+        <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>524</v>
+        <v>381</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>525</v>
+        <v>382</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10527,16 +10613,20 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>164</v>
+        <v>559</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
       </c>
@@ -10560,13 +10650,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10584,7 +10674,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>166</v>
+        <v>558</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10593,10 +10683,10 @@
         <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>83</v>
@@ -10608,10 +10698,10 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>167</v>
+        <v>392</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10622,14 +10712,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>527</v>
+        <v>562</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>140</v>
+        <v>394</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10648,18 +10738,20 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>142</v>
+        <v>395</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>169</v>
+        <v>396</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10683,13 +10775,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10707,7 +10799,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>173</v>
+        <v>562</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10719,7 +10811,7 @@
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>83</v>
@@ -10728,31 +10820,31 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>167</v>
+        <v>403</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>528</v>
+        <v>563</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>464</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10765,25 +10857,25 @@
         <v>83</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>465</v>
+        <v>564</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>466</v>
+        <v>565</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>144</v>
+        <v>456</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>150</v>
+        <v>457</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10832,7 +10924,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>467</v>
+        <v>563</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10844,7 +10936,7 @@
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -10856,10 +10948,10 @@
         <v>83</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>138</v>
+        <v>460</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10870,21 +10962,23 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>83</v>
@@ -10896,19 +10990,19 @@
         <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>185</v>
+        <v>453</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>272</v>
+        <v>522</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10918,7 +11012,7 @@
         <v>83</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>83</v>
@@ -10933,11 +11027,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>533</v>
+        <v>83</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10955,13 +11051,13 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>83</v>
@@ -10970,22 +11066,22 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>83</v>
+        <v>567</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>277</v>
+        <v>524</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>278</v>
+        <v>525</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>83</v>
@@ -10993,10 +11089,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11016,23 +11112,19 @@
         <v>83</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>374</v>
+        <v>163</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>536</v>
+        <v>164</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -11068,17 +11160,19 @@
         <v>83</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AC72" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>535</v>
+        <v>166</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11090,7 +11184,7 @@
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -11099,40 +11193,38 @@
         <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>382</v>
+        <v>167</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -11141,23 +11233,21 @@
         <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>536</v>
+        <v>142</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>376</v>
+        <v>169</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>83</v>
       </c>
@@ -11181,11 +11271,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>557</v>
+        <v>83</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -11203,19 +11295,19 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>535</v>
+        <v>173</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
@@ -11224,62 +11316,62 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>382</v>
+        <v>167</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>540</v>
+        <v>465</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>541</v>
+        <v>466</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>542</v>
+        <v>144</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>388</v>
+        <v>150</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11304,13 +11396,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11328,19 +11420,19 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>539</v>
+        <v>467</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11352,10 +11444,10 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -11366,21 +11458,21 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -11389,22 +11481,22 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>395</v>
+        <v>530</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>396</v>
+        <v>531</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>397</v>
+        <v>532</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>398</v>
+        <v>272</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11414,7 +11506,7 @@
         <v>83</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>83</v>
+        <v>572</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>83</v>
@@ -11429,13 +11521,11 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>400</v>
+        <v>533</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11453,13 +11543,13 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>83</v>
@@ -11474,27 +11564,27 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>401</v>
+        <v>534</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>402</v>
+        <v>277</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>403</v>
+        <v>278</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11505,7 +11595,7 @@
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>83</v>
@@ -11517,20 +11607,16 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>545</v>
+        <v>164</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>83</v>
       </c>
@@ -11578,19 +11664,19 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>544</v>
+        <v>166</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>83</v>
@@ -11602,10 +11688,10 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>460</v>
+        <v>167</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -11616,16 +11702,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11641,23 +11725,21 @@
         <v>83</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>453</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>519</v>
+        <v>142</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>520</v>
+        <v>169</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>83</v>
       </c>
@@ -11693,19 +11775,19 @@
         <v>83</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>518</v>
+        <v>173</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11717,10 +11799,10 @@
         <v>83</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>562</v>
+        <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>83</v>
@@ -11729,10 +11811,10 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>524</v>
+        <v>83</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>525</v>
+        <v>167</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>83</v>
@@ -11743,10 +11825,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11754,7 +11836,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>95</v>
@@ -11766,19 +11848,23 @@
         <v>83</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>163</v>
+        <v>538</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>164</v>
+        <v>539</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11826,19 +11912,19 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>166</v>
+        <v>543</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11850,10 +11936,10 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>83</v>
+        <v>544</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>167</v>
+        <v>545</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -11864,21 +11950,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11887,21 +11973,23 @@
         <v>83</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>142</v>
+        <v>547</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>169</v>
+        <v>548</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -11949,19 +12037,19 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>173</v>
+        <v>551</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11973,10 +12061,10 @@
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>83</v>
+        <v>552</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>167</v>
+        <v>553</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -11987,45 +12075,45 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>464</v>
+        <v>83</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>141</v>
+        <v>374</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>465</v>
+        <v>555</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>466</v>
+        <v>376</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>144</v>
+        <v>556</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>150</v>
+        <v>378</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12062,31 +12150,29 @@
         <v>83</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>467</v>
+        <v>554</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>83</v>
@@ -12095,35 +12181,37 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>138</v>
+        <v>382</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>95</v>
@@ -12141,16 +12229,16 @@
         <v>185</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>530</v>
+        <v>555</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>531</v>
+        <v>376</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>272</v>
+        <v>378</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12160,7 +12248,7 @@
         <v>83</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>567</v>
+        <v>83</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>83</v>
@@ -12179,7 +12267,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>533</v>
+        <v>580</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12197,10 +12285,10 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>95</v>
@@ -12218,27 +12306,27 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>534</v>
+        <v>557</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>277</v>
+        <v>381</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>278</v>
+        <v>382</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12258,22 +12346,22 @@
         <v>83</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>374</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>376</v>
+        <v>560</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12298,29 +12386,31 @@
         <v>83</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AC82" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12329,7 +12419,7 @@
         <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>107</v>
@@ -12341,40 +12431,38 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>381</v>
+        <v>138</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12383,22 +12471,22 @@
         <v>83</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>185</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>536</v>
+        <v>395</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>537</v>
+        <v>397</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12423,11 +12511,13 @@
         <v>83</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>570</v>
+        <v>400</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12445,13 +12535,13 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
@@ -12466,27 +12556,27 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>538</v>
+        <v>401</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12497,7 +12587,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12509,19 +12599,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>542</v>
+        <v>456</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>388</v>
+        <v>457</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12546,13 +12636,13 @@
         <v>83</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12570,16 +12660,16 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>107</v>
@@ -12594,10 +12684,10 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>138</v>
+        <v>459</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>392</v>
+        <v>460</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12608,14 +12698,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>585</v>
+      </c>
       <c r="D85" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12631,22 +12723,22 @@
         <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>185</v>
+        <v>453</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>395</v>
+        <v>519</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>396</v>
+        <v>520</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>397</v>
+        <v>521</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>398</v>
+        <v>522</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12671,13 +12763,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12695,7 +12787,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12710,33 +12802,33 @@
         <v>107</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>83</v>
+        <v>585</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>402</v>
+        <v>524</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>403</v>
+        <v>525</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12747,7 +12839,7 @@
         <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>83</v>
@@ -12759,20 +12851,16 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>545</v>
+        <v>164</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12820,19 +12908,19 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>544</v>
+        <v>166</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12844,10 +12932,10 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>460</v>
+        <v>167</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>83</v>
@@ -12858,23 +12946,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
@@ -12883,23 +12969,21 @@
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>453</v>
+        <v>141</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>519</v>
+        <v>142</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>520</v>
+        <v>169</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12947,7 +13031,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>518</v>
+        <v>173</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12959,10 +13043,10 @@
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>575</v>
+        <v>83</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>83</v>
@@ -12971,10 +13055,10 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>524</v>
+        <v>83</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>525</v>
+        <v>167</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>83</v>
@@ -12985,42 +13069,46 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>164</v>
+        <v>465</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>83</v>
       </c>
@@ -13068,19 +13156,19 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>166</v>
+        <v>467</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13095,7 +13183,7 @@
         <v>83</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>83</v>
@@ -13106,21 +13194,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>83</v>
@@ -13129,21 +13217,23 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>142</v>
+        <v>530</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>169</v>
+        <v>531</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13152,7 +13242,7 @@
         <v>83</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>83</v>
+        <v>590</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>83</v>
@@ -13167,13 +13257,11 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>83</v>
+        <v>533</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13191,19 +13279,19 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>173</v>
+        <v>529</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
@@ -13212,16 +13300,16 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>83</v>
+        <v>534</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>83</v>
+        <v>277</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>83</v>
@@ -13229,46 +13317,42 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>464</v>
+        <v>83</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>465</v>
+        <v>164</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>83</v>
       </c>
@@ -13316,19 +13400,19 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>467</v>
+        <v>166</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
@@ -13343,7 +13427,7 @@
         <v>83</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13354,21 +13438,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>83</v>
@@ -13377,23 +13461,21 @@
         <v>83</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>530</v>
+        <v>142</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>531</v>
+        <v>169</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13402,7 +13484,7 @@
         <v>83</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>580</v>
+        <v>83</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>83</v>
@@ -13417,41 +13499,43 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>533</v>
+        <v>83</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>529</v>
+        <v>173</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>83</v>
@@ -13460,16 +13544,16 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>534</v>
+        <v>83</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>278</v>
+        <v>167</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>83</v>
@@ -13477,10 +13561,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13488,7 +13572,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>95</v>
@@ -13503,19 +13587,19 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>582</v>
+        <v>538</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>376</v>
+        <v>540</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>378</v>
+        <v>542</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13564,13 +13648,13 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>83</v>
@@ -13585,27 +13669,27 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>381</v>
+        <v>544</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>382</v>
+        <v>545</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13625,22 +13709,22 @@
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>388</v>
+        <v>550</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13665,13 +13749,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13689,7 +13773,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13698,7 +13782,7 @@
         <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>107</v>
@@ -13713,10 +13797,10 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>138</v>
+        <v>552</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>392</v>
+        <v>553</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -13727,21 +13811,21 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>83</v>
@@ -13750,22 +13834,22 @@
         <v>83</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>185</v>
+        <v>374</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>395</v>
+        <v>555</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>397</v>
+        <v>556</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13790,37 +13874,35 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>83</v>
@@ -13835,29 +13917,31 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>401</v>
+        <v>557</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>404</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13866,7 +13950,7 @@
         <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>83</v>
@@ -13875,22 +13959,22 @@
         <v>83</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>546</v>
+        <v>376</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>456</v>
+        <v>556</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>457</v>
+        <v>378</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13915,13 +13999,11 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>83</v>
+        <v>597</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13939,13 +14021,13 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>83</v>
@@ -13960,18 +14042,2006 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="AN95" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AO95" t="s" s="2">
+      <c r="AO98" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AP95" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
+      <c r="AP98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ100" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ102" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y103" s="2"/>
+      <c r="Z103" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AQ103" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ104" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ105" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ106" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ107" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ108" t="s" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ109" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ110" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ111" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4449" uniqueCount="620">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1890,6 +1890,9 @@
     <t>Observation.component:diplome.value[x]</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Observation.component:diplome.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -1949,6 +1952,12 @@
   <si>
     <t xml:space="preserve">Quantity
 </t>
+  </si>
+  <si>
+    <t>Observation.component:volumeScolarisation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
   </si>
   <si>
     <t>Observation.component:volumeScolarisation.dataAbsentReason</t>
@@ -2259,7 +2268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ111"/>
+  <dimension ref="A1:AQ112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="68.7265625" customWidth="true" bestFit="true"/>
@@ -13837,7 +13846,7 @@
         <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>374</v>
+        <v>185</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>555</v>
@@ -13893,7 +13902,7 @@
         <v>83</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>172</v>
+        <v>596</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>554</v>
@@ -13934,7 +13943,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>554</v>
@@ -13947,7 +13956,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>95</v>
@@ -14003,7 +14012,7 @@
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -14059,7 +14068,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>558</v>
@@ -14184,7 +14193,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>562</v>
@@ -14309,7 +14318,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>563</v>
@@ -14434,13 +14443,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>518</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>83</v>
@@ -14538,7 +14547,7 @@
         <v>107</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>83</v>
@@ -14561,7 +14570,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>526</v>
@@ -14682,7 +14691,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>527</v>
@@ -14805,7 +14814,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>528</v>
@@ -14930,7 +14939,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>529</v>
@@ -14978,7 +14987,7 @@
         <v>83</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>83</v>
@@ -15053,7 +15062,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>535</v>
@@ -15174,7 +15183,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>536</v>
@@ -15297,7 +15306,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>537</v>
@@ -15422,7 +15431,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>546</v>
@@ -15547,7 +15556,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>554</v>
@@ -15573,7 +15582,7 @@
         <v>96</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>555</v>
@@ -15622,16 +15631,14 @@
         <v>83</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>83</v>
+        <v>596</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>554</v>
@@ -15672,18 +15679,20 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C109" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="D109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>95</v>
@@ -15695,22 +15704,22 @@
         <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>185</v>
+        <v>614</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>560</v>
+        <v>376</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15735,13 +15744,13 @@
         <v>83</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15759,7 +15768,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15768,7 +15777,7 @@
         <v>95</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>107</v>
@@ -15780,38 +15789,38 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>83</v>
+        <v>557</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>138</v>
+        <v>381</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>83</v>
@@ -15826,16 +15835,16 @@
         <v>185</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>395</v>
+        <v>559</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>396</v>
+        <v>560</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>397</v>
+        <v>561</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15863,10 +15872,10 @@
         <v>190</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -15884,16 +15893,16 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>107</v>
@@ -15905,31 +15914,31 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>402</v>
+        <v>138</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15948,19 +15957,19 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>564</v>
+        <v>395</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>565</v>
+        <v>396</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>456</v>
+        <v>397</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>457</v>
+        <v>398</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15985,13 +15994,13 @@
         <v>83</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16009,7 +16018,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16030,18 +16039,143 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AN111" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ111" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AO111" t="s" s="2">
+      <c r="AO112" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AP111" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ111" t="s" s="2">
+      <c r="AP112" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ112" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4449" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4449" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>TDDUI Obervation Periode Scolaire</t>
+    <t>TDDUI Observation Periode Scolaire</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -910,6 +910,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>Usager</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1830,6 +1833,9 @@
     <t>Observation.component:typeEnseignementSpecialise.value[x]</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Observation.component:typeEnseignementSpecialise.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -1888,9 +1894,6 @@
   </si>
   <si>
     <t>Observation.component:diplome.value[x]</t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Observation.component:diplome.value[x]:valueCodeableConcept</t>
@@ -5385,22 +5388,22 @@
         <v>107</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>83</v>
@@ -5408,10 +5411,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5434,16 +5437,16 @@
         <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5493,7 +5496,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5520,10 +5523,10 @@
         <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5531,14 +5534,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5557,19 +5560,19 @@
         <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5618,7 +5621,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5636,19 +5639,19 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>83</v>
@@ -5656,14 +5659,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5682,19 +5685,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5731,7 +5734,7 @@
         <v>83</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5741,7 +5744,7 @@
         <v>172</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5759,19 +5762,19 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5779,16 +5782,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5810,16 +5813,16 @@
         <v>214</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5868,7 +5871,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5886,19 +5889,19 @@
         <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>83</v>
@@ -5906,10 +5909,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6027,10 +6030,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6150,10 +6153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6176,16 +6179,16 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6235,7 +6238,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6244,13 +6247,13 @@
         <v>95</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
@@ -6259,10 +6262,10 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -6273,10 +6276,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6299,23 +6302,23 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R33" t="s" s="2">
         <v>83</v>
@@ -6360,7 +6363,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6369,13 +6372,13 @@
         <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
@@ -6384,10 +6387,10 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6398,10 +6401,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6424,16 +6427,16 @@
         <v>96</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6483,7 +6486,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6507,13 +6510,13 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>83</v>
@@ -6521,10 +6524,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6547,17 +6550,17 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6594,7 +6597,7 @@
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -6604,7 +6607,7 @@
         <v>172</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6622,19 +6625,19 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>83</v>
@@ -6642,13 +6645,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>83</v>
@@ -6670,17 +6673,17 @@
         <v>96</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6729,7 +6732,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6744,22 +6747,22 @@
         <v>107</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
@@ -6767,13 +6770,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>83</v>
@@ -6795,17 +6798,17 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6854,7 +6857,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6869,22 +6872,22 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -6892,10 +6895,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6918,19 +6921,19 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6979,7 +6982,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6988,7 +6991,7 @@
         <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>107</v>
@@ -7000,27 +7003,27 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7046,16 +7049,16 @@
         <v>185</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7083,10 +7086,10 @@
         <v>190</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -7104,7 +7107,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7113,7 +7116,7 @@
         <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>107</v>
@@ -7131,7 +7134,7 @@
         <v>138</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -7142,14 +7145,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7171,16 +7174,16 @@
         <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7208,10 +7211,10 @@
         <v>190</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7229,7 +7232,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7250,27 +7253,27 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7293,19 +7296,19 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7354,7 +7357,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7369,7 +7372,7 @@
         <v>107</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
@@ -7378,10 +7381,10 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7392,10 +7395,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7421,13 +7424,13 @@
         <v>185</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7453,13 +7456,13 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7477,7 +7480,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7498,27 +7501,27 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7544,16 +7547,16 @@
         <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7578,13 +7581,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7602,7 +7605,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7626,10 +7629,10 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7640,10 +7643,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7666,16 +7669,16 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7725,7 +7728,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7746,27 +7749,27 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7789,16 +7792,16 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7848,7 +7851,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7869,27 +7872,27 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7912,19 +7915,19 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7973,7 +7976,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7985,7 +7988,7 @@
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7997,10 +8000,10 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -8011,10 +8014,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8132,10 +8135,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8255,14 +8258,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8284,10 +8287,10 @@
         <v>141</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>144</v>
@@ -8342,7 +8345,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8380,10 +8383,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8406,13 +8409,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8463,7 +8466,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8472,7 +8475,7 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
@@ -8487,10 +8490,10 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8501,10 +8504,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8527,13 +8530,13 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8584,7 +8587,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8593,7 +8596,7 @@
         <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>107</v>
@@ -8608,10 +8611,10 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8622,10 +8625,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8651,16 +8654,16 @@
         <v>185</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8688,10 +8691,10 @@
         <v>119</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8709,7 +8712,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8730,13 +8733,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8747,10 +8750,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8776,16 +8779,16 @@
         <v>185</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8810,13 +8813,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8834,7 +8837,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8855,13 +8858,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8872,10 +8875,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8898,17 +8901,17 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8957,7 +8960,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8984,7 +8987,7 @@
         <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8995,10 +8998,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9024,10 +9027,10 @@
         <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9078,7 +9081,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9102,10 +9105,10 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9116,10 +9119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9142,16 +9145,16 @@
         <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9201,7 +9204,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9225,10 +9228,10 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9239,10 +9242,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9265,16 +9268,16 @@
         <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9324,7 +9327,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9348,10 +9351,10 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9362,10 +9365,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9388,19 +9391,19 @@
         <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9437,7 +9440,7 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
@@ -9447,7 +9450,7 @@
         <v>172</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9471,10 +9474,10 @@
         <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -9485,10 +9488,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9606,10 +9609,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9729,14 +9732,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9758,10 +9761,10 @@
         <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>144</v>
@@ -9816,7 +9819,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9854,10 +9857,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9883,13 +9886,13 @@
         <v>185</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>272</v>
@@ -9921,7 +9924,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9939,7 +9942,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>95</v>
@@ -9960,7 +9963,7 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>277</v>
@@ -9977,10 +9980,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10098,10 +10101,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10221,10 +10224,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10247,19 +10250,19 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -10308,7 +10311,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10332,10 +10335,10 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10346,10 +10349,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10375,16 +10378,16 @@
         <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10433,7 +10436,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10457,10 +10460,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10471,10 +10474,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10497,19 +10500,19 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10558,7 +10561,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10579,27 +10582,27 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10625,16 +10628,16 @@
         <v>185</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10662,10 +10665,10 @@
         <v>190</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10683,7 +10686,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10692,7 +10695,7 @@
         <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>107</v>
@@ -10710,7 +10713,7 @@
         <v>138</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10721,14 +10724,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10750,16 +10753,16 @@
         <v>185</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10787,10 +10790,10 @@
         <v>190</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10808,7 +10811,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10829,27 +10832,27 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10875,16 +10878,16 @@
         <v>84</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10933,7 +10936,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10957,10 +10960,10 @@
         <v>83</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10971,13 +10974,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>83</v>
@@ -10999,19 +11002,19 @@
         <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11060,7 +11063,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11075,7 +11078,7 @@
         <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>83</v>
@@ -11084,10 +11087,10 @@
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -11098,10 +11101,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11219,10 +11222,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11342,14 +11345,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11371,10 +11374,10 @@
         <v>141</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>144</v>
@@ -11429,7 +11432,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11467,10 +11470,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11496,13 +11499,13 @@
         <v>185</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>272</v>
@@ -11515,7 +11518,7 @@
         <v>83</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>83</v>
@@ -11534,7 +11537,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11552,7 +11555,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>95</v>
@@ -11573,7 +11576,7 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>277</v>
@@ -11590,10 +11593,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11711,10 +11714,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11834,10 +11837,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11860,19 +11863,19 @@
         <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11921,7 +11924,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11945,10 +11948,10 @@
         <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -11959,10 +11962,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11988,16 +11991,16 @@
         <v>163</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -12046,7 +12049,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12070,10 +12073,10 @@
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -12084,10 +12087,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12110,19 +12113,19 @@
         <v>96</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>374</v>
+        <v>185</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12159,17 +12162,17 @@
         <v>83</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>172</v>
+        <v>579</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12190,37 +12193,37 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>95</v>
@@ -12238,16 +12241,16 @@
         <v>185</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12276,7 +12279,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12294,7 +12297,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12315,27 +12318,27 @@
         <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12361,16 +12364,16 @@
         <v>185</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12398,10 +12401,10 @@
         <v>190</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12419,7 +12422,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12428,7 +12431,7 @@
         <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>107</v>
@@ -12446,7 +12449,7 @@
         <v>138</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12457,14 +12460,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12486,16 +12489,16 @@
         <v>185</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12523,10 +12526,10 @@
         <v>190</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12544,7 +12547,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12565,27 +12568,27 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12611,16 +12614,16 @@
         <v>84</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12669,7 +12672,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12693,10 +12696,10 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>83</v>
@@ -12707,13 +12710,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>83</v>
@@ -12735,19 +12738,19 @@
         <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12796,7 +12799,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12811,7 +12814,7 @@
         <v>107</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>83</v>
@@ -12820,10 +12823,10 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -12834,10 +12837,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12955,10 +12958,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13078,14 +13081,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13107,10 +13110,10 @@
         <v>141</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>144</v>
@@ -13165,7 +13168,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -13203,10 +13206,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13232,13 +13235,13 @@
         <v>185</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>272</v>
@@ -13251,7 +13254,7 @@
         <v>83</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>83</v>
@@ -13270,7 +13273,7 @@
       </c>
       <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>83</v>
@@ -13288,7 +13291,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>95</v>
@@ -13309,7 +13312,7 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>277</v>
@@ -13326,10 +13329,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13447,10 +13450,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13570,10 +13573,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13596,19 +13599,19 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13657,7 +13660,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13681,10 +13684,10 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -13695,10 +13698,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13724,16 +13727,16 @@
         <v>163</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13782,7 +13785,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13806,10 +13809,10 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -13820,10 +13823,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13849,16 +13852,16 @@
         <v>185</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13895,17 +13898,17 @@
         <v>83</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13926,30 +13929,30 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>83</v>
@@ -13974,16 +13977,16 @@
         <v>185</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -14012,7 +14015,7 @@
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -14030,7 +14033,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14051,27 +14054,27 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14097,16 +14100,16 @@
         <v>185</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14134,10 +14137,10 @@
         <v>190</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -14155,7 +14158,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14164,7 +14167,7 @@
         <v>95</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>107</v>
@@ -14182,7 +14185,7 @@
         <v>138</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14193,14 +14196,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14222,16 +14225,16 @@
         <v>185</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14259,10 +14262,10 @@
         <v>190</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -14280,7 +14283,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14301,27 +14304,27 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14347,16 +14350,16 @@
         <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14405,7 +14408,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14429,10 +14432,10 @@
         <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
@@ -14443,13 +14446,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>83</v>
@@ -14471,19 +14474,19 @@
         <v>96</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14532,7 +14535,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14547,7 +14550,7 @@
         <v>107</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>83</v>
@@ -14556,10 +14559,10 @@
         <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
@@ -14570,10 +14573,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14691,10 +14694,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14814,14 +14817,14 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14843,10 +14846,10 @@
         <v>141</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>144</v>
@@ -14901,7 +14904,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14939,10 +14942,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14968,13 +14971,13 @@
         <v>185</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>272</v>
@@ -14987,7 +14990,7 @@
         <v>83</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>83</v>
@@ -15006,7 +15009,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -15024,7 +15027,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>95</v>
@@ -15045,7 +15048,7 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>277</v>
@@ -15062,10 +15065,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15183,10 +15186,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15306,10 +15309,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15332,19 +15335,19 @@
         <v>96</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15393,7 +15396,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15417,10 +15420,10 @@
         <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
@@ -15431,10 +15434,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15460,16 +15463,16 @@
         <v>163</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15518,7 +15521,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15542,10 +15545,10 @@
         <v>83</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15556,10 +15559,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15582,19 +15585,19 @@
         <v>96</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15631,17 +15634,17 @@
         <v>83</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AC108" s="2"/>
       <c r="AD108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15662,30 +15665,30 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>83</v>
@@ -15707,19 +15710,19 @@
         <v>96</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15768,7 +15771,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15789,27 +15792,27 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15835,16 +15838,16 @@
         <v>185</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15872,10 +15875,10 @@
         <v>190</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>83</v>
@@ -15893,7 +15896,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15902,7 +15905,7 @@
         <v>95</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>107</v>
@@ -15920,7 +15923,7 @@
         <v>138</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -15931,14 +15934,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15960,16 +15963,16 @@
         <v>185</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15997,10 +16000,10 @@
         <v>190</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -16018,7 +16021,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16039,27 +16042,27 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16085,16 +16088,16 @@
         <v>84</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -16143,7 +16146,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16167,10 +16170,10 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-periode-scolaire.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
